--- a/public/tableau_synthese_2026.xlsx
+++ b/public/tableau_synthese_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D14A6D04-20BD-4DF3-A6B2-9B0D43548185}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3E78C1DB-F019-435C-960B-01DE6D3C41CD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,6 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Tableau de synthèse Épreuve E4'!$A$1:$H$29</definedName>
   </definedNames>
   <calcPr calcId="101716"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
       <x14:workbookPr defaultImageDpi="32767"/>
@@ -117,9 +116,6 @@
   </si>
   <si>
     <t>Conception et développement du site internet E-Ensiegnement avec le CMS WordPresse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adresse URL Portfolio : </t>
   </si>
   <si>
     <t>SESSION 2026</t>
@@ -275,6 +271,9 @@
   <si>
     <t xml:space="preserve">                                                                   Réalisation en cours de formation
 </t>
+  </si>
+  <si>
+    <t>Adresse URL Portfolio : https://portfolio-bts-pecciixwe-jiane77s-projects.vercel.app/</t>
   </si>
 </sst>
 </file>
@@ -1313,7 +1312,7 @@
       <c r="E1" s="40"/>
       <c r="F1" s="40"/>
       <c r="G1" s="40" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H1" s="40"/>
     </row>
@@ -1331,14 +1330,14 @@
     </row>
     <row r="3" spans="1:43" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="41" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B3" s="42"/>
       <c r="C3" s="42"/>
       <c r="D3" s="42"/>
       <c r="E3" s="43"/>
       <c r="F3" s="47" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G3" s="48"/>
       <c r="H3" s="49"/>
@@ -1348,7 +1347,7 @@
     </row>
     <row r="4" spans="1:43" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="44" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B4" s="45"/>
       <c r="C4" s="45"/>
@@ -1366,7 +1365,7 @@
     </row>
     <row r="5" spans="1:43" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="60" t="s">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="B5" s="61"/>
       <c r="C5" s="61"/>
@@ -1461,7 +1460,7 @@
     </row>
     <row r="8" spans="1:43" s="2" customFormat="1" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="51" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B8" s="52"/>
       <c r="C8" s="52"/>
@@ -1606,7 +1605,7 @@
     </row>
     <row r="11" spans="1:43" s="2" customFormat="1" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B11" s="14">
         <v>45942</v>
@@ -1655,7 +1654,7 @@
     </row>
     <row r="12" spans="1:43" s="2" customFormat="1" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B12" s="14">
         <v>45953</v>
@@ -1704,7 +1703,7 @@
     </row>
     <row r="13" spans="1:43" s="2" customFormat="1" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B13" s="14">
         <v>45352</v>
@@ -1753,7 +1752,7 @@
     </row>
     <row r="14" spans="1:43" s="2" customFormat="1" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B14" s="17">
         <v>45597</v>
@@ -1802,7 +1801,7 @@
     </row>
     <row r="15" spans="1:43" s="2" customFormat="1" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B15" s="17">
         <v>45992</v>
@@ -1851,7 +1850,7 @@
     </row>
     <row r="16" spans="1:43" s="2" customFormat="1" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B16" s="17">
         <v>45931</v>
@@ -1900,7 +1899,7 @@
     </row>
     <row r="17" spans="1:43" s="2" customFormat="1" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B17" s="17">
         <v>46054</v>
@@ -1949,7 +1948,7 @@
     </row>
     <row r="18" spans="1:43" s="2" customFormat="1" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B18" s="17"/>
       <c r="C18" s="4"/>
@@ -1996,7 +1995,7 @@
     </row>
     <row r="19" spans="1:43" s="2" customFormat="1" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="54" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B19" s="55"/>
       <c r="C19" s="55"/>
@@ -2043,7 +2042,7 @@
     </row>
     <row r="20" spans="1:43" s="2" customFormat="1" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="36" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B20" s="36"/>
       <c r="C20" s="36"/>
@@ -2090,7 +2089,7 @@
     </row>
     <row r="21" spans="1:43" s="2" customFormat="1" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B21" s="16"/>
       <c r="C21" s="16"/>
@@ -2137,7 +2136,7 @@
     </row>
     <row r="22" spans="1:43" s="2" customFormat="1" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="23" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B22" s="16"/>
       <c r="C22" s="16"/>
@@ -2184,7 +2183,7 @@
     </row>
     <row r="23" spans="1:43" s="2" customFormat="1" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B23" s="16"/>
       <c r="C23" s="16"/>
@@ -2231,7 +2230,7 @@
     </row>
     <row r="24" spans="1:43" s="2" customFormat="1" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B24" s="16"/>
       <c r="C24" s="16"/>
@@ -2278,7 +2277,7 @@
     </row>
     <row r="25" spans="1:43" s="2" customFormat="1" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B25" s="16"/>
       <c r="C25" s="16"/>
@@ -2325,7 +2324,7 @@
     </row>
     <row r="26" spans="1:43" s="2" customFormat="1" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B26" s="16"/>
       <c r="C26" s="16"/>
@@ -2372,7 +2371,7 @@
     </row>
     <row r="27" spans="1:43" s="2" customFormat="1" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="54" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B27" s="55"/>
       <c r="C27" s="55"/>
@@ -2419,7 +2418,7 @@
     </row>
     <row r="28" spans="1:43" s="2" customFormat="1" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="37" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B28" s="38"/>
       <c r="C28" s="38"/>
@@ -2466,7 +2465,7 @@
     </row>
     <row r="29" spans="1:43" s="2" customFormat="1" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="30"/>
@@ -2513,7 +2512,7 @@
     </row>
     <row r="30" spans="1:43" customFormat="1" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="26" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B30" s="27"/>
       <c r="C30" s="27"/>
@@ -2525,7 +2524,7 @@
     </row>
     <row r="31" spans="1:43" customFormat="1" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B31" s="28"/>
       <c r="C31" s="28"/>
@@ -2537,7 +2536,7 @@
     </row>
     <row r="32" spans="1:43" customFormat="1" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="24" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B32" s="28"/>
       <c r="C32" s="28"/>
@@ -2549,7 +2548,7 @@
     </row>
     <row r="33" spans="1:8" customFormat="1" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="24" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B33" s="31"/>
       <c r="C33" s="35"/>
@@ -2561,7 +2560,7 @@
     </row>
     <row r="34" spans="1:8" customFormat="1" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="24" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B34" s="28"/>
       <c r="C34" s="28"/>
@@ -2573,7 +2572,7 @@
     </row>
     <row r="35" spans="1:8" customFormat="1" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="24" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B35" s="28"/>
       <c r="C35" s="28"/>
@@ -2585,7 +2584,7 @@
     </row>
     <row r="36" spans="1:8" customFormat="1" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="24" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B36" s="28"/>
       <c r="C36" s="28"/>
@@ -2678,6 +2677,17 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="191d0fcf-6d89-4c90-807a-10f37b8d7a4c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="9a7dc87b-2be1-4fee-871a-355a79ca984c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F136CB4AE69C04489071CEF15422A7D7" ma:contentTypeVersion="10" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="886fd2e30fa2cc1fdb685626e6ee64a7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="191d0fcf-6d89-4c90-807a-10f37b8d7a4c" xmlns:ns3="9a7dc87b-2be1-4fee-871a-355a79ca984c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4d458b4e84b684dffe91b93afc291e76" ns2:_="" ns3:_="">
     <xsd:import namespace="191d0fcf-6d89-4c90-807a-10f37b8d7a4c"/>
@@ -2866,17 +2876,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="191d0fcf-6d89-4c90-807a-10f37b8d7a4c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="9a7dc87b-2be1-4fee-871a-355a79ca984c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12891FC5-B985-42D8-BB15-5428EFF482F5}">
   <ds:schemaRefs>
@@ -2886,6 +2885,23 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4B2C3C2-98C5-40C9-936C-A0749252C73F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="191d0fcf-6d89-4c90-807a-10f37b8d7a4c"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="9a7dc87b-2be1-4fee-871a-355a79ca984c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{115E9D4D-BBFA-4016-A3EB-D1328016C37C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2902,21 +2918,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4B2C3C2-98C5-40C9-936C-A0749252C73F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="9a7dc87b-2be1-4fee-871a-355a79ca984c"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="191d0fcf-6d89-4c90-807a-10f37b8d7a4c"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/public/tableau_synthese_2026.xlsx
+++ b/public/tableau_synthese_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3E78C1DB-F019-435C-960B-01DE6D3C41CD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{ADB6D48C-C733-4B7E-864D-3EB33293F170}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -273,7 +273,7 @@
 </t>
   </si>
   <si>
-    <t>Adresse URL Portfolio : https://portfolio-bts-pecciixwe-jiane77s-projects.vercel.app/</t>
+    <t>Adresse URL Portfolio : https://portfolio-bts-sio-phi.vercel.app/</t>
   </si>
 </sst>
 </file>
@@ -2668,26 +2668,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="191d0fcf-6d89-4c90-807a-10f37b8d7a4c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="9a7dc87b-2be1-4fee-871a-355a79ca984c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F136CB4AE69C04489071CEF15422A7D7" ma:contentTypeVersion="10" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="886fd2e30fa2cc1fdb685626e6ee64a7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="191d0fcf-6d89-4c90-807a-10f37b8d7a4c" xmlns:ns3="9a7dc87b-2be1-4fee-871a-355a79ca984c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4d458b4e84b684dffe91b93afc291e76" ns2:_="" ns3:_="">
     <xsd:import namespace="191d0fcf-6d89-4c90-807a-10f37b8d7a4c"/>
@@ -2876,32 +2856,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12891FC5-B985-42D8-BB15-5428EFF482F5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="191d0fcf-6d89-4c90-807a-10f37b8d7a4c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="9a7dc87b-2be1-4fee-871a-355a79ca984c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4B2C3C2-98C5-40C9-936C-A0749252C73F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="191d0fcf-6d89-4c90-807a-10f37b8d7a4c"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="9a7dc87b-2be1-4fee-871a-355a79ca984c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{115E9D4D-BBFA-4016-A3EB-D1328016C37C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2918,4 +2893,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4B2C3C2-98C5-40C9-936C-A0749252C73F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="191d0fcf-6d89-4c90-807a-10f37b8d7a4c"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="9a7dc87b-2be1-4fee-871a-355a79ca984c"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12891FC5-B985-42D8-BB15-5428EFF482F5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>